--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU02/HRM/post DFS_HRM-2031-0360/Panel 7/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU02/HRM/post DFS_HRM-2031-0360/Panel 7/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.82333</v>
+        <v>16.96475</v>
       </c>
       <c r="D2" t="n">
-        <v>16.39053</v>
+        <v>16.3544</v>
       </c>
       <c r="E2" t="n">
-        <v>16.67187</v>
+        <v>16.76897</v>
       </c>
       <c r="F2" t="n">
-        <v>43.12171</v>
+        <v>42.32725</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04992</v>
+        <v>0.05088</v>
       </c>
       <c r="H2" t="n">
-        <v>1.84904</v>
+        <v>1.82122</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.61039</v>
+        <v>17.00038</v>
       </c>
       <c r="D3" t="n">
-        <v>16.47856</v>
+        <v>16.70805</v>
       </c>
       <c r="E3" t="n">
-        <v>16.80182</v>
+        <v>16.76857</v>
       </c>
       <c r="F3" t="n">
-        <v>42.69232</v>
+        <v>43.01428</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05276</v>
+        <v>0.05043</v>
       </c>
       <c r="H3" t="n">
-        <v>1.82848</v>
+        <v>1.82164</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.78639</v>
+        <v>16.93451</v>
       </c>
       <c r="D4" t="n">
-        <v>16.60523</v>
+        <v>16.87729</v>
       </c>
       <c r="E4" t="n">
-        <v>16.52322</v>
+        <v>16.88813</v>
       </c>
       <c r="F4" t="n">
-        <v>42.82546</v>
+        <v>42.76307</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05216</v>
+        <v>0.04962</v>
       </c>
       <c r="H4" t="n">
-        <v>1.81671</v>
+        <v>1.81073</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.99487</v>
+        <v>16.69275</v>
       </c>
       <c r="D6" t="n">
-        <v>15.73305</v>
+        <v>15.84219</v>
       </c>
       <c r="E6" t="n">
-        <v>16.46013</v>
+        <v>16.42201</v>
       </c>
       <c r="F6" t="n">
-        <v>22.18504</v>
+        <v>21.74131</v>
       </c>
       <c r="G6" t="n">
-        <v>33.31861</v>
+        <v>33.45934</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.60336</v>
+        <v>16.66619</v>
       </c>
       <c r="D7" t="n">
-        <v>16.02164</v>
+        <v>15.991</v>
       </c>
       <c r="E7" t="n">
-        <v>16.7832</v>
+        <v>16.16891</v>
       </c>
       <c r="F7" t="n">
-        <v>22.09612</v>
+        <v>21.8545</v>
       </c>
       <c r="G7" t="n">
-        <v>34.14251</v>
+        <v>33.3149</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.41858</v>
+        <v>16.91772</v>
       </c>
       <c r="D8" t="n">
-        <v>15.9346</v>
+        <v>16.29484</v>
       </c>
       <c r="E8" t="n">
-        <v>16.18695</v>
+        <v>16.35804</v>
       </c>
       <c r="F8" t="n">
-        <v>21.79787</v>
+        <v>22.05019</v>
       </c>
       <c r="G8" t="n">
-        <v>35.11934</v>
+        <v>34.23565</v>
       </c>
     </row>
   </sheetData>
